--- a/output/pdf_financials_xlsx/RUM.xlsx
+++ b/output/pdf_financials_xlsx/RUM.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,6 +455,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -469,15 +479,17 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>43.970823</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>48.428493</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>43.222133</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>41.476067</v>
       </c>
     </row>
     <row r="5">
@@ -486,15 +498,17 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>34.283909</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>37.543209</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>33.745773</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>31.938602</v>
       </c>
     </row>
     <row r="6">
@@ -503,15 +517,17 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>9.686914</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>10.885284</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>9.47636</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>9.537464999999999</v>
       </c>
     </row>
     <row r="7">
@@ -520,15 +536,17 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -537,15 +555,17 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -554,15 +574,17 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -571,15 +593,17 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -588,15 +612,17 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>2.831929</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>4.096455</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>9.47636</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>9.537464999999999</v>
       </c>
     </row>
     <row r="12">
@@ -605,15 +631,17 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -622,15 +650,17 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -639,15 +669,17 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -656,15 +688,17 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-0.00207</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-0.001261</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-2.5e-05</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-3.7e-05</v>
       </c>
     </row>
     <row r="16">
@@ -673,15 +707,17 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>2.838038</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>1.520605</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>0.329763</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>0.388074</v>
       </c>
     </row>
     <row r="17">
@@ -690,15 +726,17 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -717,6 +755,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -734,6 +782,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E19" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -751,6 +809,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -758,15 +826,17 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -775,15 +845,17 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -792,15 +864,17 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>2.838038</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>1.520605</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>0.329763</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>0.388074</v>
       </c>
     </row>
     <row r="24">
@@ -809,15 +883,17 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="25">
@@ -826,15 +902,17 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.01</v>
       </c>
     </row>
     <row r="26">
@@ -843,12 +921,18 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
+      <c r="B26" s="3" t="n">
+        <v>29.275661</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>47.489937</v>
+      </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E26" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -860,15 +944,17 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>2.838038</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1.520605</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>0.329763</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.388074</v>
       </c>
     </row>
     <row r="28">
@@ -877,15 +963,17 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0.318948</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0.26136</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0.233263</v>
       </c>
     </row>
     <row r="29">
@@ -894,15 +982,17 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>3.282098</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1.839553</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>0.591123</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>0.621337</v>
       </c>
     </row>
     <row r="30">
@@ -911,15 +1001,17 @@
           <t>EBITDA Margin %</t>
         </is>
       </c>
-      <c r="B30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C30" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B30" s="3" t="n">
+        <v>7.464263291137398</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>3.798493172191007</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1.367639584099193</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1.498061520635503</v>
       </c>
     </row>
     <row r="31">
@@ -928,15 +1020,17 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -945,15 +1039,17 @@
           <t>Net Margin %</t>
         </is>
       </c>
-      <c r="B32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C32" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B32" s="3" t="n">
+        <v>6.454366341971812</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>3.139897415350092</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>0.7629493898415426</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>0.9356576649372275</v>
       </c>
     </row>
     <row r="33">
@@ -975,6 +1071,12 @@
       <c r="C34" s="3" t="n">
         <v>0.146992</v>
       </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -982,15 +1084,17 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -999,15 +1103,17 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0.253219</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0.146992</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1022,6 +1128,12 @@
       <c r="C37" s="3" t="n">
         <v>0.4382</v>
       </c>
+      <c r="D37" s="3" t="n">
+        <v>0.443694</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0.392294</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1029,15 +1141,17 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1049,10 +1163,14 @@
       <c r="B39" s="3" t="n">
         <v>0.029807</v>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1061,15 +1179,17 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1078,15 +1198,17 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.358043</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.4382</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.443694</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.392294</v>
       </c>
     </row>
     <row r="42">
@@ -1095,15 +1217,17 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1112,15 +1236,17 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1129,15 +1255,17 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1146,15 +1274,17 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1163,15 +1293,17 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1186,6 +1318,12 @@
       <c r="C47" s="3" t="n">
         <v>4.797145</v>
       </c>
+      <c r="D47" s="3" t="n">
+        <v>4.651879</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>4.125631</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1193,15 +1331,17 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0.249022</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0.121994</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.39291</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0.571868</v>
       </c>
     </row>
     <row r="49">
@@ -1210,15 +1350,17 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>5.875655</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>5.504331</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>5.488483</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>5.089793</v>
       </c>
     </row>
     <row r="50">
@@ -1227,15 +1369,17 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1244,15 +1388,17 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1261,15 +1407,17 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1278,15 +1426,17 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1295,15 +1445,17 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1322,6 +1474,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E55" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1329,15 +1491,17 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1346,15 +1510,17 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1364,10 +1530,16 @@
         </is>
       </c>
       <c r="B58" s="3" t="n">
-        <v>1.913468</v>
+        <v>15.017249</v>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1.559727</v>
+        <v>15.067925</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>11.957041</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>11.238299</v>
       </c>
     </row>
     <row r="59">
@@ -1376,15 +1548,17 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0.050669</v>
       </c>
     </row>
     <row r="60">
@@ -1399,6 +1573,12 @@
       <c r="C60" s="3" t="n">
         <v>6.21541</v>
       </c>
+      <c r="D60" s="3" t="n">
+        <v>6.188382</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>6.188382</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1406,15 +1586,17 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>5.875655</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>5.504331</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>5.632622</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>5.30892</v>
       </c>
     </row>
     <row r="62">
@@ -1423,15 +1605,17 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>27.200723</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>26.787666</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>23.778045</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>22.78627</v>
       </c>
     </row>
     <row r="63">
@@ -1440,15 +1624,17 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>33.076378</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>32.291997</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>29.266528</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>27.876063</v>
       </c>
     </row>
     <row r="64">
@@ -1457,15 +1643,17 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1474,15 +1662,17 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1491,15 +1681,17 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1508,15 +1700,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1531,6 +1725,12 @@
       <c r="C68" s="3" t="n">
         <v>0.554186</v>
       </c>
+      <c r="D68" s="3" t="n">
+        <v>0.470846</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.571493</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1538,15 +1738,17 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1555,15 +1757,17 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1572,15 +1776,17 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1589,15 +1795,17 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1606,15 +1814,17 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1623,15 +1833,17 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1640,15 +1852,17 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>9.662720999999999</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>6.840062</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>3.659353</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>3.004845</v>
       </c>
     </row>
     <row r="76">
@@ -1657,15 +1871,17 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>10.018138</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>7.394248</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>4.130199</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>3.576338</v>
       </c>
     </row>
     <row r="77">
@@ -1674,15 +1890,17 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1691,15 +1909,17 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1708,15 +1928,17 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1735,6 +1957,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E80" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1742,15 +1974,17 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1759,15 +1993,17 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1776,15 +2012,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1793,15 +2031,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1810,15 +2050,17 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>21.714389</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>19.780727</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>15.291675</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>13.836838</v>
       </c>
     </row>
     <row r="86">
@@ -1827,15 +2069,17 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>21.714389</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>19.780727</v>
+      </c>
+      <c r="D86" s="3" t="n">
+        <v>15.291675</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>13.836838</v>
       </c>
     </row>
     <row r="87">
@@ -1844,15 +2088,17 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>31.732527</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>27.174975</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>19.421874</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>17.413176</v>
       </c>
     </row>
     <row r="88">
@@ -1861,15 +2107,17 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>7.377311</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>7.377311</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>7.427311</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>7.427311</v>
       </c>
     </row>
     <row r="89">
@@ -1878,15 +2126,17 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1901,6 +2151,12 @@
       <c r="C90" s="3" t="n">
         <v>-1.385283</v>
       </c>
+      <c r="D90" s="3" t="n">
+        <v>0.034911</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>0.497973</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -1908,15 +2164,17 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1931,6 +2189,12 @@
       <c r="C92" s="3" t="n">
         <v>1.014911</v>
       </c>
+      <c r="D92" s="3" t="n">
+        <v>1.024148</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>1.024148</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -1938,15 +2202,17 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1955,15 +2221,17 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>5.486334</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>7.006939</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>8.486370000000001</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>8.949432</v>
       </c>
     </row>
     <row r="95">
@@ -1972,15 +2240,17 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1989,15 +2259,17 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>5.486334</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>7.006939</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>8.486370000000001</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>8.949432</v>
       </c>
     </row>
     <row r="97">
@@ -2006,15 +2278,17 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.16586864498888</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.2169868590041056</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.2899684581649043</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.3210436136551995</v>
       </c>
     </row>
     <row r="98">
@@ -2030,15 +2304,17 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>2.838038</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>1.520605</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>0.329763</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>0.388074</v>
       </c>
     </row>
     <row r="100">
@@ -2047,15 +2323,17 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2064,15 +2342,17 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2081,15 +2361,17 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2098,15 +2380,17 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2115,15 +2399,17 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2132,15 +2418,17 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2149,15 +2437,17 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.065634</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.438575</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.103469</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.611188</v>
       </c>
     </row>
     <row r="107">
@@ -2166,15 +2456,17 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.059237</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2183,15 +2475,17 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2200,15 +2494,17 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2217,15 +2513,17 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2240,6 +2538,12 @@
       <c r="C111" s="3" t="n">
         <v>-0.060769</v>
       </c>
+      <c r="D111" s="3" t="n">
+        <v>-0.08812399999999999</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.15487</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -2247,15 +2551,17 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2264,15 +2570,17 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2281,15 +2589,17 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2298,15 +2608,17 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2315,15 +2627,17 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2332,15 +2646,17 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2349,15 +2665,17 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2372,6 +2690,12 @@
       <c r="C119" s="3" t="n">
         <v>0.080715</v>
       </c>
+      <c r="D119" s="3" t="n">
+        <v>-0.037008</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.205539</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -2379,15 +2703,17 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2396,15 +2722,17 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2413,15 +2741,17 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2430,15 +2760,17 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2447,15 +2779,17 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2464,15 +2798,17 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2481,15 +2817,17 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2508,6 +2846,16 @@
           <t>-</t>
         </is>
       </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E127" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2515,15 +2863,17 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -2538,6 +2888,12 @@
       <c r="C129" s="3" t="n">
         <v>-4.277507</v>
       </c>
+      <c r="D129" s="3" t="n">
+        <v>-1.818765</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-1.872307</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -2551,6 +2907,12 @@
       <c r="C130" s="3" t="n">
         <v>0.253219</v>
       </c>
+      <c r="D130" s="3" t="n">
+        <v>0.118015</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>0.146918</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -2558,15 +2920,17 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2575,15 +2939,17 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.037312</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>-0.106227</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>0.028903</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>0.119985</v>
       </c>
     </row>
     <row r="133">
@@ -2598,6 +2964,12 @@
       <c r="C133" s="3" t="n">
         <v>0.146992</v>
       </c>
+      <c r="D133" s="3" t="n">
+        <v>0.146918</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>0.266903</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -2605,15 +2977,17 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>-0.081521</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>-0.060769</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>-0.08812399999999999</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-0.15487</v>
       </c>
     </row>
     <row r="135">
@@ -2622,15 +2996,17 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>1.984271</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>4.029796</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>1.796552</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>2.042961</v>
       </c>
     </row>
   </sheetData>
@@ -2644,7 +3020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:H128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2684,6 +3060,16 @@
           <t>2020</t>
         </is>
       </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2694,14 +3080,24 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dec 31, 2020 Dec</t>
+          <t>Dec 31, 2023 Dec</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="F2" s="5" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>3.1e-05</v>
       </c>
     </row>
@@ -2718,19 +3114,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>CashAndCashEquivalents</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>0.253219</v>
-      </c>
-      <c r="F3" s="5" t="n">
-        <v>0.146992</v>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.146918</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.266903</v>
       </c>
     </row>
     <row r="4">
@@ -2760,6 +3166,12 @@
       <c r="F4" s="5" t="n">
         <v>0.4382</v>
       </c>
+      <c r="G4" s="5" t="n">
+        <v>0.443694</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>0.392294</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2774,19 +3186,29 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>Inventory 4</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t>Inventory</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Inventory</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
-        <v>5.015371</v>
-      </c>
-      <c r="F5" s="5" t="n">
-        <v>4.797145</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>4.651879</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>4.125631</v>
       </c>
     </row>
     <row r="6">
@@ -2816,6 +3238,12 @@
       <c r="F6" s="5" t="n">
         <v>0.121994</v>
       </c>
+      <c r="G6" s="5" t="n">
+        <v>0.245992</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.304965</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2830,21 +3258,25 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Current portion of loans receivable 5</t>
+          <t>CURRENT total</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LoansReceivable</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.029807</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>5.875655</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>5.504331</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>5.488483</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>5.089793</v>
       </c>
     </row>
     <row r="8">
@@ -2855,20 +3287,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CURRENT total</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" s="5" t="n">
-        <v>5.875655</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>5.504331</v>
+          <t>Property and equipment 6</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>1.229236</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>1.148304</v>
       </c>
     </row>
     <row r="9">
@@ -2884,19 +3330,31 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>PROPERTY AND EQUIPMENT 7</t>
+          <t>Intangible assets 7</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NetPPE</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>1.913468</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>1.559727</v>
+          <t>OtherIntangibleAssets</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.050669</v>
       </c>
     </row>
     <row r="10">
@@ -2912,7 +3370,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GOODWILL 8</t>
+          <t>Goodwill 8</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2920,11 +3378,21 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>6.307819</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>6.21541</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>6.188382</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>6.188382</v>
       </c>
     </row>
     <row r="11">
@@ -2940,15 +3408,29 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>RIGHT-OF-USE ASSETS 16</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" s="5" t="n">
-        <v>13.103781</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>13.508198</v>
+          <t>Deferred tax assets 10</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DeferredTaxAssets</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.144139</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.219127</v>
       </c>
     </row>
     <row r="12">
@@ -2964,15 +3446,29 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NON-CURRENT total</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" s="5" t="n">
-        <v>27.200723</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>26.787666</v>
+          <t>Right-of-use-assets 14</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>10.727805</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>10.089995</v>
       </c>
     </row>
     <row r="13">
@@ -2983,24 +3479,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CURRENT</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>NON-CURRENT total</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PayablesAndAccruedExpenses</t>
+          <t>TotalNonCurrentAssets</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.355417</v>
+        <v>27.200723</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.554186</v>
+        <v>26.787666</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>23.778045</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>22.78627</v>
       </c>
     </row>
     <row r="14">
@@ -3016,15 +3518,25 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Goods and services tax payable</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
-        <v>0.075864</v>
+        <v>0.355417</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.08037999999999999</v>
+        <v>0.554186</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.470846</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.571493</v>
       </c>
     </row>
     <row r="15">
@@ -3040,15 +3552,21 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Current portion of lease liabilities 16</t>
+          <t>Goods and services tax payable</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="5" t="n">
-        <v>1.731967</v>
+        <v>0.075864</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>1.551951</v>
+        <v>0.08037999999999999</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.073738</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.065604</v>
       </c>
     </row>
     <row r="16">
@@ -3076,6 +3594,12 @@
       <c r="F16" s="5" t="n">
         <v>2.257731</v>
       </c>
+      <c r="G16" s="5" t="n">
+        <v>1.622322</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.052185</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3090,15 +3614,25 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bank loan 9</t>
+          <t>Current portion of bank loan 9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
-      <c r="E17" s="5" t="n">
-        <v>7.85489</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>2.95</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.519487</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0.559472</v>
       </c>
     </row>
     <row r="18">
@@ -3109,20 +3643,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NON-CURRENT</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LEASE LIABILITIES 18</t>
+          <t>Current portion of lease liabilities 14</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" s="5" t="n">
-        <v>11.696251</v>
-      </c>
-      <c r="F18" s="5" t="n">
-        <v>12.386479</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>1.443806</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>1.327584</v>
       </c>
     </row>
     <row r="19">
@@ -3133,24 +3677,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Share capital 12</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="n">
-        <v>7.377311</v>
-      </c>
-      <c r="F19" s="5" t="n">
-        <v>7.377311</v>
+          <t>Bank loan 9</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.952005</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0.400027</v>
       </c>
     </row>
     <row r="20">
@@ -3161,24 +3711,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contributed surplus 13</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>AdditionalPaidInCapital</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>1.014911</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>1.014911</v>
+          <t>Lease liabilities 14</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>10.209471</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>9.860473000000001</v>
       </c>
     </row>
     <row r="21">
@@ -3194,19 +3750,29 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Accumulated deficit</t>
+          <t>Share capital 11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>-2.905888</v>
-      </c>
-      <c r="F21" s="5" t="n">
-        <v>-1.385283</v>
+          <t>CapitalStock</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>7.427311</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>7.427311</v>
       </c>
     </row>
     <row r="22">
@@ -3222,186 +3788,282 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY total</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" s="5" t="n">
-        <v>5.486334</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>7.006939</v>
+          <t>Contributed surplus</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>1.024148</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>1.024148</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SHAREHOLDERS' EQUITY</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dec 31, 2020 Dec</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="n">
-        <v>0.002019</v>
-      </c>
-      <c r="F23" s="5" t="n">
-        <v>3.1e-05</v>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.034911</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.497973</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Net comprehensive income</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>SHAREHOLDERS' EQUITY total</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E24" s="5" t="n">
-        <v>2.838038</v>
+        <v>5.486334</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>1.520605</v>
+        <v>7.006939</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>8.486370000000001</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>8.949432</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Property and equipment depreciation 7</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
+          <t>Dec 31, 2020 Dec</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" s="5" t="n">
-        <v>0.44406</v>
+        <v>0.002019</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.318948</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Loss on disposal of property and equipment and goodwill</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>Cash and cash equivalents</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CashAndCashEquivalents</t>
+        </is>
+      </c>
       <c r="E26" s="5" t="n">
-        <v>0.00347</v>
+        <v>0.253219</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.046487</v>
+        <v>0.146992</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Right-of-use assets depreciation 16</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Inventory</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>1.385303</v>
+        <v>5.015371</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>1.139645</v>
+        <v>4.797145</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Finance costs on lease liabilities 16</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Current portion of loans receivable 5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LoansReceivable</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>0.658183</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0.626305</v>
+        <v>0.029807</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Notional accretive interest 11</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>PROPERTY AND EQUIPMENT 7</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
-        <v>0.143915</v>
-      </c>
-      <c r="F29" t="inlineStr">
+        <v>1.913468</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1.559727</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3410,24 +4072,36 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gain on redemption of convertible debenture 11</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>GOODWILL 8</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
       <c r="E30" s="5" t="n">
-        <v>-3.472811</v>
-      </c>
-      <c r="F30" t="inlineStr">
+        <v>6.307819</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>6.21541</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3436,181 +4110,255 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital 17</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
+          <t>RIGHT-OF-USE ASSETS 16</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
-        <v>0.065634</v>
+        <v>13.103781</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.438575</v>
+        <v>13.508198</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Cash flow from operating activities</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Current portion of lease liabilities 16</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
       <c r="E32" s="5" t="n">
-        <v>2.065792</v>
+        <v>1.731967</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>4.090565</v>
+        <v>1.551951</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Purchase of property and equipment 7</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PurchaseOfPPE</t>
-        </is>
-      </c>
+          <t>Bank loan 9</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>-0.081521</v>
+        <v>7.85489</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.060769</v>
+        <v>2.95</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>NON-CURRENT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Proceeds on disposal of property and equipment</t>
+          <t>LEASE LIABILITIES 18</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="5" t="n">
-        <v>0.01054</v>
+        <v>11.696251</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.141484</v>
+        <v>12.386479</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Cash flow from investing activities</t>
+          <t>Share capital 12</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-0.070981</v>
+        <v>7.377311</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.080715</v>
+        <v>7.377311</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Repayment of loans receivable 5</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>Contributed surplus 13</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E36" s="5" t="n">
-        <v>0.015257</v>
+        <v>1.014911</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.029807</v>
+        <v>1.014911</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Repayments of operating facility and bank loan 9</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Accumulated deficit</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E37" s="5" t="n">
-        <v>-0.236348</v>
+        <v>-2.905888</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>-2.647159</v>
+        <v>-1.385283</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3619,22 +4367,28 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lease payments 16</t>
+          <t>Dec 31, 2023 Dec</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" s="5" t="n">
-        <v>-1.719048</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>-1.660155</v>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="39">
@@ -3645,22 +4399,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Convertible debenture redemption transaction costs 11</t>
+          <t>Net comprehensive income</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="5" t="n">
-        <v>-0.091984</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.838038</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>1.520605</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.277529</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.463062</v>
       </c>
     </row>
     <row r="40">
@@ -3671,24 +4429,34 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cash flow used in financing activities</t>
+          <t>Property and equipment depreciation 6</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="n">
-        <v>-2.032123</v>
-      </c>
-      <c r="F40" s="5" t="n">
-        <v>-4.277507</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.26136</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.233263</v>
       </c>
     </row>
     <row r="41">
@@ -3699,20 +4467,36 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DECREASE IN CASH</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" s="5" t="n">
-        <v>-0.037312</v>
-      </c>
-      <c r="F41" s="5" t="n">
-        <v>-0.106227</v>
+          <t>Intangible assets depreciation 7</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.001273</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3723,24 +4507,30 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CASH AND CASH EQUIVALENTS - BEGINNING OF YEAR</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="n">
-        <v>0.290531</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>0.253219</v>
+          <t>Loss (gain) on disposal of property and equipment and goodwill 6</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>-0.004172</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0.002539</v>
       </c>
     </row>
     <row r="43">
@@ -3751,24 +4541,30 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CASH AND CASH EQUIVALENTS - END OF YEAR</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="n">
-        <v>0.253219</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>0.146992</v>
+          <t>Deferred income tax (recovery) expense 10</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.052234</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>-0.074988</v>
       </c>
     </row>
     <row r="44">
@@ -3779,20 +4575,34 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CASH FLOWS SUPPLEMENTARY INFORMATION</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Interest paid</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>0.834859</v>
-      </c>
-      <c r="F44" s="5" t="n">
-        <v>0.4073</v>
+          <t>Right-of-use assets depreciation 14</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>1.133746</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0.962767</v>
       </c>
     </row>
     <row r="45">
@@ -3803,21 +4613,3007 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Share based payments 11, 12</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.059237</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital 15</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.103469</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0.611188</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Cash flow from operating activities</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>2.065792</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>4.090565</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>1.884676</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>2.197831</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Purchase of property and equipment 6</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>-0.08812399999999999</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>-0.15487</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Purchase of intangible assets 7</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>-0.050669</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Proceeds on disposal of goodwill 8</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.027028</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Proceeds on disposal of property and equipment</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" s="5" t="n">
+        <v>0.01054</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.141484</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.024088</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Cash flow used in investing activities</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.037008</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-0.205539</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Principal repayments on bank loan 9</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.731647</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>-0.511993</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Proceeds from operating facility 9</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>15.814219</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>14.303674</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Principal repayments on operating facility 9</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-16.053568</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>-14.873811</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Principal portion of lease liabilities 14</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.847769</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>-0.790177</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Cash flow used in financing activities</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>-2.032123</v>
+      </c>
+      <c r="F57" s="5" t="n">
+        <v>-4.277507</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-1.818765</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>-1.872307</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>INCREASE IN CASH</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.028903</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>0.119985</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CASH - BEGINNING OF YEAR</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.118015</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>0.146918</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>CASH - END OF YEAR</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.146918</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>0.266903</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>CASH FLOWS SUPPLEMENTARY INFORMATION</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Interest paid on bank loan, operating facility and other</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.260146</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>0.284924</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>CASH FLOWS SUPPLEMENTARY INFORMATION</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Interest paid on leases liabilities</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.632749</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>0.586359</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>CASH FLOWS SUPPLEMENTARY INFORMATION</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
         <is>
           <t>Income taxes paid</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr"/>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Dec 31, 2020 Dec</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Property and equipment depreciation 7</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>0.318948</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Loss on disposal of property and equipment and goodwill</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>0.00347</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.046487</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Right-of-use assets depreciation 16</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>1.385303</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>1.139645</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Finance costs on lease liabilities 16</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" s="5" t="n">
+        <v>0.658183</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>0.626305</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Notional accretive interest 11</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>0.143915</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Gain on redemption of convertible debenture 11</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>-3.472811</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Items not affecting cash</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Changes in non-cash working capital 17</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.065634</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>0.438575</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Purchase of property and equipment 7</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>-0.081521</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-0.060769</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Cash flow from investing activities</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>-0.070981</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>0.080715</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Repayment of loans receivable 5</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.015257</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>0.029807</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Repayments of operating facility and bank loan 9</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" s="5" t="n">
+        <v>-0.236348</v>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>-2.647159</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Lease payments 16</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>-1.719048</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>-1.660155</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Convertible debenture redemption transaction costs 11</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>-0.091984</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DECREASE IN CASH</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>-0.037312</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-0.106227</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>CASH AND CASH EQUIVALENTS - BEGINNING OF YEAR</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0.290531</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>0.253219</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>CASH AND CASH EQUIVALENTS - END OF YEAR</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>0.253219</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>0.146992</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CASH FLOWS SUPPLEMENTARY INFORMATION</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Interest paid</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" s="5" t="n">
+        <v>0.834859</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Dec 31, 2023 Dec</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>43.222133</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>41.476067</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Cost of sales 4</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>33.745773</v>
+      </c>
+      <c r="H84" s="5" t="n">
+        <v>31.938602</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Restated total</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>9.47636</v>
+      </c>
+      <c r="H85" s="5" t="n">
+        <v>9.537464999999999</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Operating and administrative expenses 17</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>6.854485</v>
+      </c>
+      <c r="H86" s="5" t="n">
+        <v>7.070873</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Income from operations before depreciation and other</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>2.621875</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>2.466592</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Property and equipment depreciation 6</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.26136</v>
+      </c>
+      <c r="H88" s="5" t="n">
+        <v>0.233263</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Intangible asset depreciation 7</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.001273</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Right-of-use equipment depreciation 14</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>1.133746</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>0.962767</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Restated</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Finance costs on lease liabilities 14</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.632749</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>0.586359</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Finance costs</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.260146</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>0.284924</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Loss (gain) on disposal of property and equipment and goodwill 5, 6</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-0.004172</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>0.002539</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Store closure expenses</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.007035</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>0.008703000000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-2.5e-05</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>-3.7e-05</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Other expenses (income) total</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>2.292112</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>2.078518</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Income before tax</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.329763</v>
+      </c>
+      <c r="H97" s="5" t="n">
+        <v>0.388074</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Deferred income tax (recovery) expense 10</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.052234</v>
+      </c>
+      <c r="H98" s="5" t="n">
+        <v>-0.074988</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Net comprehensive income</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.277529</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>0.463062</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Basic income per share 13</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Other expenses (income)</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Diluted income per share 13</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Dec 31, 2020 Dec</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SALES</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="n">
+        <v>43.970823</v>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>48.428493</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>COST OF SALES 4</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>CostOfRevenue</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>34.283909</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>37.543209</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Note total</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" s="5" t="n">
+        <v>9.686914</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>10.885284</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>OPERATING AND ADMINISTRATIVE EXPENSES</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>6.854985</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>6.788829</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>INCOME FROM OPERATIONS</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>OperatingIncome</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="n">
+        <v>2.831929</v>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>4.096455</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>PROPERTY AND EQUIPTMENT DEPRECIATION 7</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>0.44406</v>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>0.318948</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>RIGHT-OF-USE ASSETS DEPRECIATION 16</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E109" s="5" t="n">
+        <v>1.385303</v>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>1.139645</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>FINANCE COSTS ON LEASE LIABILITIES 16</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" s="5" t="n">
+        <v>0.658183</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.626305</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Finance costs 11</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" s="5" t="n">
+        <v>0.977398</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.407751</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Loss on disposal of property and equipment and goodwill</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>0.00347</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.046487</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Store closure expenses</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" s="5" t="n">
+        <v>0.000358</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>0.037975</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>-0.00207</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>-0.001261</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Gain on redemption of convertible debenture 12</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>-3.472811</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME) total</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" s="5" t="n">
+        <v>-0.006109</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>2.57585</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>INCOME BEFORE TAX</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>2.838038</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>1.520605</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>INCOME TAXES 10</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>NET COMPREHENSIVE INCOME</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" s="5" t="n">
+        <v>2.838038</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>1.520605</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Basic income per share 15</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" s="5" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Diluted income per share 15</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>DilutedEPS</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>1e-07</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>3e-08</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares - basic</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>BasicAverageShares</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>29.275661</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>47.489937</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>OTHER EXPENSES (INCOME)</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Weighted average number of shares - diluted</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>DilutedAverageShares</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="n">
+        <v>29.275661</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>47.489937</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>11. FINANCE COSTS</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Bank loan interest $</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" s="5" t="n">
+        <v>0.575306</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>0.407751</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>11. FINANCE COSTS</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Convertible debenture interest</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" s="5" t="n">
+        <v>0.258177</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>11. FINANCE COSTS</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Notional accretive interest</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" s="5" t="n">
+        <v>0.143915</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>11. FINANCE COSTS</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Total $</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" s="5" t="n">
+        <v>0.977398</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>0.407751</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>11. FINANCE COSTS</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>The Company had a $6,865,000 unsecured subordinated convertible debenture (the “Debenture”) that it redeemed on Jul</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" s="5" t="n">
+        <v>0.002019</v>
+      </c>
+      <c r="F128" s="5" t="n">
+        <v>3e-06</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/RUM.xlsx
+++ b/output/pdf_financials_xlsx/RUM.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/RUM.xlsx
+++ b/output/pdf_financials_xlsx/RUM.xlsx
@@ -658,16 +658,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -734,16 +734,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -5272,7 +5272,11 @@
           <t>Income taxes paid</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>IncomeTaxPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -5922,7 +5926,11 @@
           <t>Interest paid</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>InterestPaidSupplementalData</t>
+        </is>
+      </c>
       <c r="E81" s="5" t="n">
         <v>0.834859</v>
       </c>

--- a/output/pdf_financials_xlsx/RUM.xlsx
+++ b/output/pdf_financials_xlsx/RUM.xlsx
@@ -1079,10 +1079,10 @@
         <v>0.146992</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.146918</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.266903</v>
       </c>
     </row>
     <row r="35">
@@ -1117,10 +1117,10 @@
         <v>0.146992</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.146918</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.266903</v>
       </c>
     </row>
     <row r="37">
@@ -1345,10 +1345,10 @@
         <v>0.121994</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.39291</v>
+        <v>0.245992</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.571868</v>
+        <v>0.304965</v>
       </c>
     </row>
     <row r="49">
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-1.719048</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-1.660155</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-1.719048</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-1.660155</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -3126,7 +3126,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5742,7 +5742,11 @@
           <t>Lease payments 16</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E76" s="5" t="n">
         <v>-1.719048</v>
       </c>

--- a/output/pdf_financials_xlsx/RUM.xlsx
+++ b/output/pdf_financials_xlsx/RUM.xlsx
@@ -2559,13 +2559,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.01054</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.141484</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.024088</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -4850,7 +4850,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.01054</v>
       </c>

--- a/output/pdf_financials_xlsx/RUM.xlsx
+++ b/output/pdf_financials_xlsx/RUM.xlsx
@@ -740,10 +740,10 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.052234</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>0.074988</v>
       </c>
     </row>
     <row r="18">
@@ -816,15 +816,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" s="3" t="n">
+        <v>0.277529</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0.463062</v>
       </c>
     </row>
     <row r="21">
@@ -878,10 +874,10 @@
         <v>1.520605</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.329763</v>
+        <v>0.277529</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.388074</v>
+        <v>0.463062</v>
       </c>
     </row>
     <row r="24">
@@ -1034,10 +1030,10 @@
         <v>0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>15.83986074847694</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>19.32311878662317</v>
       </c>
     </row>
     <row r="32">
@@ -1053,10 +1049,10 @@
         <v>3.139897415350092</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.7629493898415426</v>
+        <v>0.6420992689092878</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>0.9356576649372275</v>
+        <v>1.116455906969193</v>
       </c>
     </row>
     <row r="33">
@@ -2318,10 +2314,10 @@
         <v>1.520605</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>0.329763</v>
+        <v>0.277529</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>0.388074</v>
+        <v>0.463062</v>
       </c>
     </row>
     <row r="100">
@@ -2644,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>0</v>
+        <v>-0.050669</v>
       </c>
     </row>
     <row r="117">
@@ -4778,7 +4774,11 @@
           <t>Purchase of intangible assets 7</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -6546,7 +6546,11 @@
           <t>Deferred income tax (recovery) expense 10</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
